--- a/data/seed/portfolio/L-2024-4345/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-4345/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I155"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -560,31 +560,31 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>14593000</v>
+        <v>41481000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4561</t>
+          <t>Предоплата за товар по дог. №141/26 от 01.07.2026</t>
         </is>
       </c>
     </row>
@@ -601,31 +601,31 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>5509000</v>
+        <v>10716000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bunyodkor Yog' Zavodi MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>257946867</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000234254733001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №268 от 01.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №151/26 от 01.07.2026</t>
         </is>
       </c>
     </row>
@@ -640,40 +640,40 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>3993000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>2748000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Urganch Farm Savdo MChJ</t>
+          <t>Farovon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>334523022</t>
+          <t>217331460</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000583829379001</t>
+          <t>20208000745840981001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4768</t>
+          <t>Оплата за товар по счет-фактуре №3939 от 01.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -682,34 +682,39 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>28800000</v>
+        <v>4748000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-4345)</t>
+          <t>Zafar Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>271861323</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16307000262176915417</t>
+          <t>20208000409780977001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-4345 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Предоплата за материалы по договору №205/26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -717,33 +722,28 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>10774000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>258540792</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-4345)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>16307000262176915417</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7240 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-4345 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
@@ -760,31 +760,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>7040000</v>
+        <v>40937000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №30/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6791</t>
         </is>
       </c>
     </row>
@@ -801,31 +801,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>5719000</v>
+        <v>7163000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №8734 ОТ 06.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7294 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -840,33 +840,33 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>2637000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>5615000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5226 за поставленный товар</t>
+          <t>Оплата за сырье по договору №137/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -882,32 +882,32 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3120000</v>
+        <v>8115000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Urganch Farm Savdo MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>334523022</t>
+          <t>297673817</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000583829379001</t>
+          <t>20208000746747794001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №230/26</t>
+          <t>Оплата за транспортные услуги по договору №5/26</t>
         </is>
       </c>
     </row>
@@ -923,32 +923,32 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>19101000</v>
+        <v>9122000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №208/26, QQS bilan</t>
+          <t>Оплата за сырье по договору №78/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Перечисление заработной платы за июнь 2026 г. соглсно реестру №7337</t>
         </is>
       </c>
     </row>
@@ -1001,31 +1001,31 @@
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>16393000</v>
+        <v>14539000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Shartnoma №276/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №85/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1041,39 +1041,39 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>15247000</v>
+        <v>3960000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №89/26</t>
+          <t>Оплата за сырье по дог. №242/26 от 07.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1082,32 +1082,32 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2717000</v>
+        <v>9410000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>252648400</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000600679341001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Предоплата за материалы по договору №175/26</t>
         </is>
       </c>
     </row>
@@ -1123,39 +1123,39 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6090000</v>
+        <v>2717000</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Xiva Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>231955422</t>
+          <t>343676893</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000886280228001</t>
+          <t>20208000136353301001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №187/26, QQS bilan</t>
+          <t>Аренда помещения за июль, дог. №6/20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1163,33 +1163,33 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>7060000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>3996000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №268/26</t>
+          <t>Оплата за продукцию по договору №217/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1204,40 +1204,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>16396000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>4133000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>252302215</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000382937982001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №157/26 от 09.07.2026</t>
+          <t>Tovarlar uchun to'lov h/f №6061</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1245,23 +1245,23 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>6504000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>33116000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>297673817</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000746747794001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1271,14 +1271,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №204/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по дог. №207/26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1288,38 +1288,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>2715000</v>
+        <v>4094000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oqtosh Mehmonxona MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>259545583</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000651710832001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4511 09.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №3484 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1327,40 +1327,40 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>30180000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>20199000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №146/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №292/26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1370,38 +1370,38 @@
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>2926000</v>
+        <v>10763000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6675 10.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №54/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1409,40 +1409,40 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>7103000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>7863000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>231955422</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000886280228001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №78/26</t>
+          <t>Оплата за товар по счет-фактуре №9226 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1452,38 +1452,38 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>2054000</v>
+        <v>3132000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bunyodkor Yog' Zavodi MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>257946867</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000234254733001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №51/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №6/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1492,39 +1492,39 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6456000</v>
+        <v>8719000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik MChJ</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>316800402</t>
+          <t>252302215</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000088408042001</t>
+          <t>20208000382937982001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №93/26, QQS BILAN</t>
+          <t>Оплата за товары согласно счет-фактуре №7752</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1534,38 +1534,38 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>4162000</v>
+        <v>15487000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Yulduz Oziq-ovqat Savdo XK</t>
+          <t>Durdona Trans Servis AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>255734893</t>
+          <t>351797699</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000660553632001</t>
+          <t>20208000584695467001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5071 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Предоплата за товар по договору №70/26 от 16.07.2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1573,40 +1573,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>4434000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>4794000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Guliston Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>373489326</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000055363253001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5299 ОТ 16.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>НДФЛ ЗА ИЮНЬ 2026</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
     </row>
@@ -1655,40 +1655,40 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>3154000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>4434000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4790 16.07.2026, QQS bilan</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1696,40 +1696,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>2545000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>11522000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Oydin Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354558376</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000171083214001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №204/26</t>
+          <t>Предоплата за товар по договору №151/26 от 17.07.2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1737,40 +1737,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>51723000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>2824000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №184/26 ОТ 16.07.2026, НДС 12%</t>
+          <t>Оплата за товар по с/ф №6806 от 17.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1780,31 +1780,31 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>8684000</v>
+        <v>28105000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Durdona Trans Servis AJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>351797699</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000584695467001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SHARTNOMA №108/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №61/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1821,21 +1821,21 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>31175000</v>
+        <v>19180000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bunyodkor Yog' Zavodi MChJ</t>
+          <t>Farovon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>257946867</t>
+          <t>217331460</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000234254733001</t>
+          <t>20208000745840981001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5594 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №6164 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1862,31 +1862,31 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>12649000</v>
+        <v>7695000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Shartnoma №64/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9426</t>
         </is>
       </c>
     </row>
@@ -1903,31 +1903,31 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>7552000</v>
+        <v>4423000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6293</t>
+          <t>Shartnoma №174/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -1944,38 +1944,38 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>3108000</v>
+        <v>3868000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9395</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1000 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>10897000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>3095000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Nurafshon Non MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>273624888</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000469474081001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5960</t>
+          <t>Оплата за товар по счет-фактуре №1261 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>21934000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>3923000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oydin Meva Eksport MChJ</t>
+          <t>Zafar Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>342173314</t>
+          <t>271861323</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000067458409001</t>
+          <t>20208000409780977001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8929 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №108/26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2066,39 +2066,39 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>10908000</v>
+        <v>21851000</v>
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Zafar Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>271861323</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000409780977001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №42/26</t>
+          <t>Оплата за транспортные услуги по договору №205/26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2106,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>4550000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>21856000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА ИЮНЬ</t>
+          <t>Оплата за продукцию по дог. №295/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>19574000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>13896000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №16/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2144</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2190,38 +2190,38 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>6927000</v>
+        <v>6228000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ilhom Un Mahsulotlari MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>395517976</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000965846954001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №79/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №65/26 от 21.07.2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,40 +2229,40 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>6486000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>4515000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №984 за поставленный товар</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2272,31 +2272,31 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>4506000</v>
+        <v>13601000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bunyodkor Yog' Zavodi MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>257946867</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000234254733001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Shartnoma №217/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №147 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2313,38 +2313,38 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>2060000</v>
+        <v>39219000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №63/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №8763 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,40 +2352,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>1698000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>13971000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Farovon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>217331460</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000293503389001</t>
+          <t>20208000745840981001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за продукцию по договору №134/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2394,39 +2394,39 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>6885000</v>
+        <v>1698000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>316800402</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000088408042001</t>
+          <t>20208000838822181001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №150/26</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2435,32 +2435,32 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>24997000</v>
+        <v>6198000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Urganch Farm Savdo MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>334523022</t>
+          <t>297673817</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000583829379001</t>
+          <t>20208000746747794001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за упаковочые материалы, с/ф №9348</t>
+          <t>Оплата за сырье по договору №208/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2475,33 +2475,33 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>69158000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>8913000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oqtosh Mehmonxona MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>259545583</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000651710832001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5202 27.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №179/26</t>
         </is>
       </c>
     </row>
@@ -2516,33 +2516,33 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>21045000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>14435000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>252302215</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000382937982001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №105/26, QQS 12%</t>
+          <t>Предоплата за материалы по дог. №124/26</t>
         </is>
       </c>
     </row>
@@ -2557,40 +2557,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>15840000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>142402000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ilhom Un Mahsulotlari MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>395517976</t>
+          <t>297673817</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000965846954001</t>
+          <t>20208000746747794001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Shartnoma №111/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №248/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2600,38 +2600,38 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>5104000</v>
+        <v>2822000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №154/26 от 27.07.2026</t>
+          <t>Оплата за товар по счет-фактуре №5135 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2639,40 +2639,40 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>6727000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>16248000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8667</t>
+          <t>Предоплата за товар по дог. №293/26 от 30.07.2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2680,40 +2680,35 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>6641000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>258540792</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6723</t>
+          <t>Комиссия за пеевод</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,38 +2718,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>4809000</v>
+        <v>38822000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Yulduz Oziq-ovqat Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>255734893</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000660553632001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №102/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №69/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2764,38 +2759,38 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>2759000</v>
+        <v>10936000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Oydin Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354558376</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000171083214001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5780 29.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №189/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2805,38 +2800,38 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>2490000</v>
+        <v>6650000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7426</t>
+          <t>Оплата за товар по счет-фактуре №5548 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2844,40 +2839,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>107501000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>6097000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6250</t>
+          <t>Shartnoma №266/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2887,38 +2882,38 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>1773000</v>
+        <v>2252000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>307106925</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000001685493001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №143</t>
+          <t>Оплата за продукцию по договору №74/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2927,39 +2922,39 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>4677000</v>
+        <v>45231000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Urganch Farm Savdo MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>334523022</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000583829379001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №238</t>
+          <t>Оплата за товары согласно с/ф №3778</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2967,40 +2962,40 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>7464000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>47614000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oqtosh Meva Eksport MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>241736248</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000874694740001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №45/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №267/26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3008,40 +3003,40 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>4484000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>30203000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Zafar Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>271861323</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000409780977001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2503 31.07.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №178/26</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3049,40 +3044,35 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>1786000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>32974000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oqtosh Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>241736248</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000874694740001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №38/26 от 31.07.2026</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3091,17 +3081,17 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>300000</v>
+        <v>28800000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-4345)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>16307000262176915417</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3111,14 +3101,14 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Kredit shartnomasi L-2024-4345 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3128,38 +3118,38 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>41579000</v>
+        <v>2594000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №69/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №4006 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3169,38 +3159,38 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>3955000</v>
+        <v>1475000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oqtosh Mehmonxona MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>259545583</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000651710832001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Shartnoma №189/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №5143 от 06.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3209,39 +3199,39 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>22761000</v>
+        <v>5134000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>316800402</t>
+          <t>297673817</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000088408042001</t>
+          <t>20208000746747794001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №76/26</t>
+          <t>Оплата за сырье по договору №276/26 от 06.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3250,34 +3240,39 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>28800000</v>
+        <v>7886000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-4345)</t>
+          <t>Sarbon Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>348400760</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>16307000262176915417</t>
+          <t>20208000679341129001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-4345 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за упаковочные материалы, с/ф №489</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3286,34 +3281,39 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>32974000</v>
+        <v>2755000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Xiva Qurilish Materiallari XK</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>343676893</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000136353301001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №4175</t>
+          <t>Аренда помещения за август, дог. №6/20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3323,31 +3323,31 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>14835000</v>
+        <v>27197000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Oydin Sut MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>287159751</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000900339523001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4006</t>
+          <t>Оплата за продукцию по договору №56/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3364,31 +3364,31 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>5609000</v>
+        <v>7543000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №268/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №218/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3403,40 +3403,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>2755000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>2496000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>252648400</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000600679341001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>Mahsulot uchun to'lov, shartnoma №268/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3446,38 +3446,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>124924000</v>
+        <v>2022000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4297</t>
+          <t>Оплата за продукцию по договору №225/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3485,40 +3485,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>14409000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>22700000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yulduz Oziq-ovqat Savdo XK</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>255734893</t>
+          <t>252302215</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000660553632001</t>
+          <t>20208000382937982001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3896 12.08.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №272/26</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,40 +3526,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>4517000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>4691000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>252302215</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000382937982001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5794 17.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №4418</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3569,38 +3569,38 @@
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>3487000</v>
+        <v>36472000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Shartnoma №261/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №4297 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3608,40 +3608,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>4496000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>32620000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Guliston Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>373489326</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000055363253001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Оплата за товар по счет-фактуре №3896 от 12.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,33 +3649,33 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>4496000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>4726000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Оплата за товар по с/ф №1259 от 12.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3690,40 +3690,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>87319000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>2610000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>307106925</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000001685493001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №142/26</t>
+          <t>Оплата за продукцию по договору №79/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,38 +3733,38 @@
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>11169000</v>
+        <v>1903000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2067 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №5794 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3774,38 +3774,38 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>6872000</v>
+        <v>1673000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №28/26, QQS 12%</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6222</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3815,38 +3815,38 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>6168000</v>
+        <v>1514000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bunyodkor Yog' Zavodi MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>257946867</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000234254733001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №82/26 от 19.08.2026</t>
+          <t>Предоплата за товар по дог. №261/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3855,39 +3855,39 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>18218000</v>
+        <v>4496000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>231955422</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000886280228001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5928</t>
+          <t>Ijtimoiy soliq iyul 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,40 +3895,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>4779000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>4496000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Shartnoma №25/26 bo'yicha oldindan to'lov</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3936,40 +3936,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>13108000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>20492000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №229/26, QQS bilan</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №28/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3977,40 +3977,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>4679000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>2159000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>QO'SHILGAN QIYMAT SOLIG'I IYUL OYI</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2067</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4020,38 +4020,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>18755000</v>
+        <v>4493000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Farovon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>217331460</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000745840981001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9802</t>
+          <t>Shartnoma №82/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4059,40 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>17827000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>7835000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bunyodkor Yog' Zavodi MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>257946867</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000234254733001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №265/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №243/26 ОТ 19.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4102,38 +4102,38 @@
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>4481000</v>
+        <v>6277000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oqtosh Mehmonxona MChJ</t>
+          <t>Oydin Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>259545583</t>
+          <t>354558376</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000651710832001</t>
+          <t>20208000171083214001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9637 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №1168 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4141,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>28903000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>4710000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №68/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №25/26 от 20.08.2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4182,40 +4182,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>41120000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>2373000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №6381</t>
+          <t>Предоплата за товар по договору №102/26 от 20.08.2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4225,38 +4225,38 @@
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>33687000</v>
+        <v>1911000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №5/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №214/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4266,38 +4266,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>4181000</v>
+        <v>1867000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zafar Avto Ehtiyot MChJ</t>
+          <t>Nurafshon Non MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>212871597</t>
+          <t>273624888</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000199003395001</t>
+          <t>20208000469474081001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Shartnoma №286/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №5525 от 21.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4305,40 +4305,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>1722000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>17594000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Farovon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>217331460</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000293503389001</t>
+          <t>20208000745840981001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Предоплата за товар по договору №130/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4346,40 +4346,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>60824000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>15060000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №137/26 от 27.08.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №9802 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4387,23 +4387,23 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>14445000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>14658000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik MChJ</t>
+          <t>Farovon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>316800402</t>
+          <t>217331460</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000088408042001</t>
+          <t>20208000745840981001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №240/26</t>
+          <t>Оплата за продукцию по дог. №265/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4430,38 +4430,38 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>64274000</v>
+        <v>7936000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Nurafshon Non MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>273624888</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000469474081001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SHARTNOMA №112/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №189/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4471,38 +4471,38 @@
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>4413000</v>
+        <v>2908000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Guliston Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>373489326</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000055363253001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9820</t>
+          <t>Предоплата за товар по дог. №224/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4511,17 +4511,22 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>300000</v>
+        <v>1722000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000838822181001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4531,14 +4536,14 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4547,39 +4552,39 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>18222000</v>
+        <v>4587000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>316800402</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000088408042001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №133/26</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4587,23 +4592,23 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>109208000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>69440000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Oqtosh Meva Eksport MChJ</t>
+          <t>Zafar Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>241736248</t>
+          <t>271861323</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000874694740001</t>
+          <t>20208000409780977001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4613,14 +4618,14 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3804 01.09.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №79/26</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4630,38 +4635,38 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>35874000</v>
+        <v>52877000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ilhom Un Mahsulotlari MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>395517976</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000965846954001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №670</t>
+          <t>Оплата за товар по с/ф №8928 от 25.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4669,23 +4674,23 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>6927000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>1896000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Nurafshon Non MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>231955422</t>
+          <t>273624888</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000886280228001</t>
+          <t>20208000469474081001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4695,14 +4700,14 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №190/26</t>
+          <t>ОПЛАТА ПО С/Ф №2413 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4710,40 +4715,40 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>7620000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>1769000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>316800402</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000088408042001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №201/26</t>
+          <t>Оплата за товар по счет-фактуре №3829 от 25.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4751,40 +4756,40 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>14381000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>21705000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7654 от 03.09.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №136/26</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4792,40 +4797,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>5017000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>1944000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Oydin Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354558376</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000171083214001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4003</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9637</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4833,35 +4838,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>29863000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>4368000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Jizzax Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Оплата за продукцию по договору №5/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4869,35 +4879,40 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>1690000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-4345)</t>
+          <t>Oydin Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>287159751</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>16307000262176915417</t>
+          <t>20208000900339523001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-4345 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Предоплата за товар по договору №286/26 от 27.08.2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4905,40 +4920,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>45190000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>14642000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №195/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8818</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4948,38 +4963,38 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>9370000</v>
+        <v>14254000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Durdona Trans Servis AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>351797699</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000584695467001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Shartnoma №84/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по с/ф №6532 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4987,40 +5002,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>2496000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>7289000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>252648400</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000600679341001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №84/24</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №112/26 ОТ 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5028,40 +5043,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>8104000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>2349000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1709</t>
+          <t>Оплата по счет-фактуре №9820 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5069,40 +5084,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>15993000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>1768000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>231955422</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000886280228001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №158/26, QQS bilan</t>
+          <t>Оплата за товар по с/ф №1059 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5111,39 +5126,34 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>16729000</v>
+        <v>300000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>316800402</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000088408042001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №279/26, QQS bilan</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5151,40 +5161,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>5915000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>7484000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4783 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №199/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5192,40 +5202,40 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>4374000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>10910000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oqtosh Meva Eksport MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>241736248</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000874694740001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Shartnoma №285/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №7183</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5233,40 +5243,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>22821000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>32501000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8433</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №48/26</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5274,40 +5284,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>2907000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>113014000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>231955422</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000886280228001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №298/26</t>
+          <t>Оплата за продукцию по договору №39/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5315,40 +5325,40 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>1999000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>2268000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №278/26</t>
+          <t>Оплата за продукцию по договору №277/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5356,40 +5366,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>4072000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>3411000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Предоплата за товар по договору №251/26 от 03.09.2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5397,40 +5407,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>4072000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>2329000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nurafshon Mebel MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>307106925</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000001685493001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5984 03.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5439,39 +5449,39 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>60822000</v>
+        <v>13465000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>316800402</t>
+          <t>297673817</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000088408042001</t>
+          <t>20208000746747794001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №81/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №30/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5480,39 +5490,39 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>2240000</v>
+        <v>17817000</v>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Zafar Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>271861323</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000409780977001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6751</t>
+          <t>Оплата за сырье по договору №218/26 от 03.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5520,40 +5530,40 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>2280000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>3848000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Farovon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>217331460</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000745840981001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №266/26</t>
+          <t>Предоплата за товар по договору №172/26 от 04.09.2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5562,39 +5572,34 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>5466000</v>
+        <v>28800000</v>
       </c>
       <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>381718613</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-4345)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>16307000262176915417</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4515</t>
+          <t>Kredit shartnomasi L-2024-4345 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5602,23 +5607,23 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>96103000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>2795000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Urganch Farm Savdo MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>334523022</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000583829379001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5628,14 +5633,14 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №234/26</t>
+          <t>Оплата за продукцию по договору №249/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5643,40 +5648,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>20743000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>2496000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Xiva Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>343676893</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000136353301001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Shartnoma №58/26 bo'yicha oldindan to'lov</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №6/20</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5685,39 +5690,34 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>17976000</v>
+        <v>29863000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>381718613</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №4432</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №6202</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,40 +5725,40 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>23527000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>60803000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oqtosh Meva Eksport MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>241736248</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000874694740001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3685 21.09.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №106/26 от 07.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5768,38 +5768,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>9497000</v>
+        <v>6666000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Oqtosh Meva Eksport MChJ</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>241736248</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000874694740001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №879</t>
+          <t>Оплата за товар по счет-фактуре №8016 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5809,38 +5809,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>6919000</v>
+        <v>2031000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Jizzax Tekstil MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №159/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №5094 от 09.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5848,40 +5848,40 @@
           <t>230</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>6774000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>8608000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5955 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №8652</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5891,38 +5891,38 @@
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>4301000</v>
+        <v>22104000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Oqtosh Meva Eksport MChJ</t>
+          <t>Nurafshon Non MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>241736248</t>
+          <t>273624888</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000874694740001</t>
+          <t>20208000469474081001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №97/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №381 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5930,40 +5930,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>2536000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>10871000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Angren Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>272996570</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000809959663001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №202/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №5274 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5971,40 +5971,40 @@
           <t>233</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>11407000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>3511000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Nurafshon Non MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>273624888</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000469474081001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №147/26</t>
+          <t>Оплата по счет-фактуре №5421 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6012,40 +6012,40 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>4307000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>4047000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nurafshon Non MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>273624888</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000469474081001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Mahsulot uchun to'lov, shartnoma №287/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6053,23 +6053,23 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>12765000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>16737000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Oqtosh Meva Eksport MChJ</t>
+          <t>Zafar Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>241736248</t>
+          <t>271861323</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000874694740001</t>
+          <t>20208000409780977001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6079,14 +6079,14 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3154 24.09.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактур №8511</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6094,23 +6094,23 @@
           <t>236</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>9617000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>25932000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>297673817</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000746747794001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6120,14 +6120,14 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №174/26 от 25.09.2026</t>
+          <t>Предоплата за материалы по договору №226/26</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6135,40 +6135,40 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>6610000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>58726000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Oqtosh Meva Eksport MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>241736248</t>
+          <t>297673817</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000874694740001</t>
+          <t>20208000746747794001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Shartnoma №281/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №185/26 от 15.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6178,38 +6178,38 @@
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>11051000</v>
+        <v>4024000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Qo'qon Savdo XK</t>
+          <t>Nurafshon Non MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>258540792</t>
+          <t>273624888</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000114538813001</t>
+          <t>20208000469474081001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9607 28.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №168/26 от 16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6218,39 +6218,39 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>1560000</v>
+        <v>4072000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000293503389001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6259,39 +6259,39 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>4019000</v>
+        <v>4072000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №164/26</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6299,40 +6299,40 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>4124000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>105832000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Nihol Non MChJ</t>
+          <t>Nurafshon Non MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>381718613</t>
+          <t>273624888</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000394097809001</t>
+          <t>20208000469474081001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4390</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9620</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6341,39 +6341,39 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>10318000</v>
+        <v>39246000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Urganch Farm Savdo MChJ</t>
+          <t>Oydin Non MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>334523022</t>
+          <t>394686762</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000583829379001</t>
+          <t>20208000425473315001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №221/26</t>
+          <t>Оплата за сырье по договору №159/26 от 17.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6381,54 +6381,505 @@
           <t>243</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>3652000</v>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Jizzax Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>354079231</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000453881363001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата по счет-фактуре №81 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="n">
-        <v>1137248000</v>
-      </c>
-      <c r="D154" s="4" t="n">
-        <v>1128048000</v>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>16972000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Nurafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>273624888</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000469474081001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №236 от 21.09.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>3347000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Jizzax Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>354079231</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000453881363001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №141/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>4095000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>НДС за август 2026 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>8483000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Jizzax Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>354079231</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000453881363001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №1028 от 2.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>2531000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Jizzax Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>354079231</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000453881363001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Shartnoma №146/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>1560000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000838822181001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>4493000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Jizzax Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>354079231</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000453881363001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №221/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>1905000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Nurafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>273624888</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000469474081001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №544 от 29.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>8390000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Jizzax Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>354079231</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000453881363001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №157/26 от 30.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>4733000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Jizzax Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>354079231</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000453881363001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №948 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Zarafshon Kredit Bank</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Комиссия за перевод</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="n">
+        <v>1108967000</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>1099767000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C155" s="4" t="n">
+      <c r="C166" s="4" t="n">
         <v>71400000</v>
       </c>
-      <c r="D155" s="4" t="n"/>
+      <c r="D166" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
